--- a/data/test_files/challenge/challenge_formulas.xlsx
+++ b/data/test_files/challenge/challenge_formulas.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="D2">
         <f>B2-C2</f>
-        <v/>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,7 @@
       </c>
       <c r="D3">
         <f>B3-C3</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -481,15 +481,15 @@
       </c>
       <c r="B4">
         <f>SUM(B2:B3)</f>
-        <v/>
+        <v>115000</v>
       </c>
       <c r="C4">
         <f>SUM(C2:C3)</f>
-        <v/>
+        <v>65000</v>
       </c>
       <c r="D4">
         <f>SUM(D2:D3)</f>
-        <v/>
+        <v>50000</v>
       </c>
     </row>
     <row r="6">
